--- a/cp-upgrade-mhd/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/cp-upgrade-mhd/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:39:30+00:00</t>
+    <t>2026-05-05T15:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
